--- a/DNDProj/output.xlsx
+++ b/DNDProj/output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A65"/>
+  <dimension ref="A1:A67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,439 +445,453 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Roman Emperor</t>
+          <t>Samantha Walker</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mary Littlelamb</t>
+          <t>David Miller</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Xylophone Player</t>
+          <t>Kelly Perez</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ellie Snellie</t>
+          <t>Jonathan Clark</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marc Vertongen</t>
+          <t>Christine Collins</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Doortje Van Hoeck</t>
+          <t>Nathan Wright</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tokio Hotelroom</t>
+          <t>Zachary Hernandez</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Lisa Davis</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stefan Van Der Giessen</t>
+          <t>Adam Edwards</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Echo Preacher</t>
+          <t> </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Xavier Waterslaeghers</t>
+          <t>Stefaan Baumont</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bryan Adams</t>
+          <t>Daniel Martin</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Hermione Granger</t>
+          <t>Amanda Wilson</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Hotel Habbo</t>
+          <t>Sean Parker</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ronald Weasley</t>
+          <t>Jennifer Brown</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gert Verhulst</t>
+          <t>Jacob Baker</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Stephanie Jackson</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sigurd Joostens</t>
+          <t>Kevin Lopez</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Balthasar Boma</t>
+          <t> </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Foxtrot Reacher</t>
+          <t>Stefan Van Der Giessen</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Stein Gatekeeper</t>
+          <t>Aaron Nelson</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Aaron Zoetedaele</t>
+          <t>Michelle Campbell</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Steve Erwin</t>
+          <t>Ryan Thompson</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Danielle Adams</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sybren Windels</t>
+          <t>Michael Jones</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Indigo Violet</t>
+          <t>Catherine Turner</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pedro Griffin</t>
+          <t>Brandon Gonzalez</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Larry Duff</t>
+          <t> </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kilo Grahamme</t>
+          <t>Sigurd Joostens</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Golf Agnew</t>
+          <t>Benjamin Mitchell</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Rachel Lee</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tanner Rawlings</t>
+          <t>Christopher Rodriguez</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Maurice de Praetere</t>
+          <t>Kayla Green</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pol De Tremmerie</t>
+          <t>James Smith</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Carmen Waterslaeghers</t>
+          <t>Robert Williams</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Hotel Hazbin</t>
+          <t> </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Niels Destadsbader</t>
+          <t>Sybren Windels</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Lauren Harris</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Solas x</t>
+          <t>Alexis King</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ulysses Lesse</t>
+          <t>Patrick Phillips</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Varian Wrynn</t>
+          <t>Ashley Anderson</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Noa Farwilliger</t>
+          <t> </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Quartz Crystalline</t>
+          <t>Tanner Rawlings</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Queen Rhapsody</t>
+          <t>Tyler Robinson</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Jessica Thomas</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Stefaan Baumont</t>
+          <t>Sarah Garcia</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Harry Potter</t>
+          <t>Maria Johnson</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Fernand Costermans</t>
+          <t> </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bieke Crucke</t>
+          <t>Solas Cooper</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Foxtrot Freeman</t>
+          <t>Emily Moore</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Pascal Smet</t>
+          <t>Jason Perez</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pascale De Backer</t>
+          <t>Nicole White</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Samuel Roberts</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ben De Saveur</t>
+          <t> </t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>echooo Preacher</t>
+          <t>Ben De Saveur</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Golf House</t>
+          <t>Andrew Hernandez</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dwayne Johnson</t>
+          <t>Diana Evans</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Rebecca Carter</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Gerard Butler</t>
+          <t>Justin Allen</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>November December</t>
+          <t> </t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Oscar Wilde</t>
+          <t>Gerard Butler</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cyrill Mcduff</t>
+          <t>Hannah Hall</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
+        <is>
+          <t>Matthew Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Joshua Taylor</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t> </t>
         </is>
